--- a/assets/libreoffice_calc_njc/dfb46a6b-3f2d-4e4a-b4ef-20997ea21563/SalesAnalysis_L3_01.xlsx
+++ b/assets/libreoffice_calc_njc/dfb46a6b-3f2d-4e4a-b4ef-20997ea21563/SalesAnalysis_L3_01.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="23">
   <si>
     <t xml:space="preserve">Month</t>
   </si>
@@ -38,24 +38,27 @@
     <t xml:space="preserve">Avg Margin %</t>
   </si>
   <si>
+    <t xml:space="preserve">Margin %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jan</t>
   </si>
   <si>
-    <t xml:space="preserve">Feb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jun</t>
-  </si>
-  <si>
     <t xml:space="preserve">Region</t>
   </si>
   <si>
@@ -75,9 +78,6 @@
   </si>
   <si>
     <t xml:space="preserve">Profit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margin %</t>
   </si>
   <si>
     <t xml:space="preserve">North</t>
@@ -96,8 +96,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -173,12 +174,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -191,6 +200,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF3D3D3D"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -199,126 +225,161 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="n">
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>9450</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>5950</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A2,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <f aca="false">ROUND(D2/B2*100,1)</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>8300</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>5200</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A3,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <f aca="false">ROUND(D3/B3*100,1)</f>
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5300</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A4,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <f aca="false">ROUND(D4/B4*100,1)</f>
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2600</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A5,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <f aca="false">ROUND(D5/B5*100,1)</f>
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>4150</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2450</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A6,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <f aca="false">ROUND(D6/B6*100,1)</f>
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="n">
         <v>5550</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C7" s="2" t="n">
         <v>3500</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D7" s="2" t="n">
         <v>2050</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E7" s="2" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A7,Sales!$I:$I),1)</f>
         <v>36.7</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>6600</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>4150</v>
-      </c>
-      <c r="D3" s="0" t="n">
-        <v>2450</v>
-      </c>
-      <c r="E3" s="0" t="n">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>8300</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>5200</v>
-      </c>
-      <c r="D4" s="0" t="n">
-        <v>3100</v>
-      </c>
-      <c r="E4" s="0" t="n">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>8400</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>5300</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>3100</v>
-      </c>
-      <c r="E5" s="0" t="n">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>7000</v>
-      </c>
-      <c r="C6" s="0" t="n">
-        <v>4400</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>2600</v>
-      </c>
-      <c r="E6" s="0" t="n">
-        <v>36.7</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>9450</v>
-      </c>
-      <c r="C7" s="0" t="n">
-        <v>5950</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E7" s="0" t="n">
-        <v>36.7</v>
+      <c r="H7" s="3" t="n">
+        <f aca="false">ROUND(D7/B7*100,1)</f>
+        <v>36.9</v>
       </c>
     </row>
   </sheetData>
@@ -343,38 +404,38 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
@@ -395,9 +456,11 @@
         <v>3150</v>
       </c>
       <c r="H2" s="1" t="n">
+        <f aca="false">F2-G2</f>
         <v>2100</v>
       </c>
       <c r="I2" s="1" t="n">
+        <f aca="false">ROUND(H2/F2*100,1)</f>
         <v>40</v>
       </c>
     </row>
@@ -424,9 +487,11 @@
         <v>3000</v>
       </c>
       <c r="H3" s="1" t="n">
+        <f aca="false">F3-G3</f>
         <v>2000</v>
       </c>
       <c r="I3" s="1" t="n">
+        <f aca="false">ROUND(H3/F3*100,1)</f>
         <v>40</v>
       </c>
     </row>
@@ -453,9 +518,11 @@
         <v>2700</v>
       </c>
       <c r="H4" s="1" t="n">
+        <f aca="false">F4-G4</f>
         <v>1800</v>
       </c>
       <c r="I4" s="1" t="n">
+        <f aca="false">ROUND(H4/F4*100,1)</f>
         <v>40</v>
       </c>
     </row>
@@ -482,15 +549,17 @@
         <v>2400</v>
       </c>
       <c r="H5" s="1" t="n">
+        <f aca="false">F5-G5</f>
         <v>1600</v>
       </c>
       <c r="I5" s="1" t="n">
+        <f aca="false">ROUND(H5/F5*100,1)</f>
         <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
@@ -511,15 +580,17 @@
         <v>2250</v>
       </c>
       <c r="H6" s="1" t="n">
+        <f aca="false">F6-G6</f>
         <v>1500</v>
       </c>
       <c r="I6" s="1" t="n">
+        <f aca="false">ROUND(H6/F6*100,1)</f>
         <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>21</v>
@@ -540,9 +611,11 @@
         <v>2800</v>
       </c>
       <c r="H7" s="1" t="n">
+        <f aca="false">F7-G7</f>
         <v>1400</v>
       </c>
       <c r="I7" s="1" t="n">
+        <f aca="false">ROUND(H7/F7*100,1)</f>
         <v>33.3</v>
       </c>
     </row>
@@ -569,15 +642,17 @@
         <v>2600</v>
       </c>
       <c r="H8" s="1" t="n">
+        <f aca="false">F8-G8</f>
         <v>1300</v>
       </c>
       <c r="I8" s="1" t="n">
+        <f aca="false">ROUND(H8/F8*100,1)</f>
         <v>33.3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
@@ -598,9 +673,11 @@
         <v>1800</v>
       </c>
       <c r="H9" s="1" t="n">
+        <f aca="false">F9-G9</f>
         <v>1200</v>
       </c>
       <c r="I9" s="1" t="n">
+        <f aca="false">ROUND(H9/F9*100,1)</f>
         <v>40</v>
       </c>
     </row>
@@ -627,9 +704,11 @@
         <v>2200</v>
       </c>
       <c r="H10" s="1" t="n">
+        <f aca="false">F10-G10</f>
         <v>1100</v>
       </c>
       <c r="I10" s="1" t="n">
+        <f aca="false">ROUND(H10/F10*100,1)</f>
         <v>33.3</v>
       </c>
     </row>
@@ -656,15 +735,17 @@
         <v>2000</v>
       </c>
       <c r="H11" s="1" t="n">
+        <f aca="false">F11-G11</f>
         <v>1000</v>
       </c>
       <c r="I11" s="1" t="n">
+        <f aca="false">ROUND(H11/F11*100,1)</f>
         <v>33.3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
@@ -685,15 +766,17 @@
         <v>1900</v>
       </c>
       <c r="H12" s="1" t="n">
+        <f aca="false">F12-G12</f>
         <v>950</v>
       </c>
       <c r="I12" s="1" t="n">
+        <f aca="false">ROUND(H12/F12*100,1)</f>
         <v>33.3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
@@ -714,9 +797,11 @@
         <v>1700</v>
       </c>
       <c r="H13" s="1" t="n">
+        <f aca="false">F13-G13</f>
         <v>850</v>
       </c>
       <c r="I13" s="1" t="n">
+        <f aca="false">ROUND(H13/F13*100,1)</f>
         <v>33.3</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/dfb46a6b-3f2d-4e4a-b4ef-20997ea21563/SalesAnalysis_L3_01.xlsx
+++ b/assets/libreoffice_calc_njc/dfb46a6b-3f2d-4e4a-b4ef-20997ea21563/SalesAnalysis_L3_01.xlsx
@@ -41,22 +41,22 @@
     <t xml:space="preserve">Margin %</t>
   </si>
   <si>
+    <t xml:space="preserve">Jan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan</t>
   </si>
   <si>
     <t xml:space="preserve">Region</t>
@@ -226,9 +226,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -244,8 +244,6 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
@@ -255,13 +253,13 @@
         <v>6</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9450</v>
+        <v>5550</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5950</v>
+        <v>3500</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3500</v>
+        <v>2050</v>
       </c>
       <c r="E2" s="2" t="n">
         <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A2,Sales!$I:$I),1)</f>
@@ -269,7 +267,7 @@
       </c>
       <c r="H2" s="3" t="n">
         <f aca="false">ROUND(D2/B2*100,1)</f>
-        <v>37</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -277,13 +275,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>8300</v>
+        <v>6600</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5200</v>
+        <v>4150</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3100</v>
+        <v>2450</v>
       </c>
       <c r="E3" s="2" t="n">
         <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A3,Sales!$I:$I),1)</f>
@@ -291,7 +289,7 @@
       </c>
       <c r="H3" s="3" t="n">
         <f aca="false">ROUND(D3/B3*100,1)</f>
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -299,10 +297,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>8400</v>
+        <v>8300</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>3100</v>
@@ -313,7 +311,7 @@
       </c>
       <c r="H4" s="3" t="n">
         <f aca="false">ROUND(D4/B4*100,1)</f>
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -321,13 +319,13 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7000</v>
+        <v>8400</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4400</v>
+        <v>5300</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>2600</v>
+        <v>3100</v>
       </c>
       <c r="E5" s="2" t="n">
         <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A5,Sales!$I:$I),1)</f>
@@ -335,7 +333,7 @@
       </c>
       <c r="H5" s="3" t="n">
         <f aca="false">ROUND(D5/B5*100,1)</f>
-        <v>37.1</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -343,13 +341,13 @@
         <v>10</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6600</v>
+        <v>7000</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>4150</v>
+        <v>4400</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2450</v>
+        <v>2600</v>
       </c>
       <c r="E6" s="2" t="n">
         <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A6,Sales!$I:$I),1)</f>
@@ -365,13 +363,13 @@
         <v>11</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5550</v>
+        <v>9450</v>
       </c>
       <c r="C7" s="2" t="n">
+        <v>5950</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>3500</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>2050</v>
       </c>
       <c r="E7" s="2" t="n">
         <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A7,Sales!$I:$I),1)</f>
@@ -379,7 +377,7 @@
       </c>
       <c r="H7" s="3" t="n">
         <f aca="false">ROUND(D7/B7*100,1)</f>
-        <v>36.9</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -404,38 +402,38 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
@@ -466,7 +464,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
@@ -497,7 +495,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
@@ -528,7 +526,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -559,7 +557,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
@@ -590,7 +588,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>21</v>
@@ -621,7 +619,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>21</v>
@@ -652,7 +650,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
@@ -683,7 +681,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>21</v>
@@ -714,7 +712,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -745,7 +743,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
@@ -776,7 +774,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>

--- a/assets/libreoffice_calc_njc/dfb46a6b-3f2d-4e4a-b4ef-20997ea21563/SalesAnalysis_L3_01.xlsx
+++ b/assets/libreoffice_calc_njc/dfb46a6b-3f2d-4e4a-b4ef-20997ea21563/SalesAnalysis_L3_01.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MonthSummary" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Sales" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="MonthSummary" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="Sales" sheetId="3" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="23">
   <si>
     <t xml:space="preserve">Month</t>
   </si>
@@ -38,46 +39,46 @@
     <t xml:space="preserve">Avg Margin %</t>
   </si>
   <si>
+    <t xml:space="preserve">Profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost</t>
+  </si>
+  <si>
     <t xml:space="preserve">Margin %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Apr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cost</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profit</t>
   </si>
   <si>
     <t xml:space="preserve">North</t>
@@ -96,9 +97,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -174,7 +176,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -183,7 +185,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -225,162 +239,9 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>5550</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>2050</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A2,Sales!$I:$I),1)</f>
-        <v>36.7</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <f aca="false">ROUND(D2/B2*100,1)</f>
-        <v>36.9</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>6600</v>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>4150</v>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2450</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A3,Sales!$I:$I),1)</f>
-        <v>36.7</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <f aca="false">ROUND(D3/B3*100,1)</f>
-        <v>37.1</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>8300</v>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>5200</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>3100</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A4,Sales!$I:$I),1)</f>
-        <v>36.7</v>
-      </c>
-      <c r="H4" s="3" t="n">
-        <f aca="false">ROUND(D4/B4*100,1)</f>
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>8400</v>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>5300</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>3100</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A5,Sales!$I:$I),1)</f>
-        <v>36.7</v>
-      </c>
-      <c r="H5" s="3" t="n">
-        <f aca="false">ROUND(D5/B5*100,1)</f>
-        <v>36.9</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>4400</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A6,Sales!$I:$I),1)</f>
-        <v>36.7</v>
-      </c>
-      <c r="H6" s="3" t="n">
-        <f aca="false">ROUND(D6/B6*100,1)</f>
-        <v>37.1</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>9450</v>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>5950</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A7,Sales!$I:$I),1)</f>
-        <v>36.7</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <f aca="false">ROUND(D7/B7*100,1)</f>
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -396,44 +257,335 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="n">
+        <f aca="false">ROUND(H2/B2*100,1)</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>5300</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <f aca="false">ROUND(D2/B2*100,1)</f>
+        <v>43.1</v>
+      </c>
+      <c r="I2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4150</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A3,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <f aca="false">B3-C3</f>
+        <v>4150</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <f aca="false">B3-C3</f>
+        <v>4150</v>
+      </c>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>9500</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A4,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <f aca="false">B4-C4</f>
+        <v>6000</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <f aca="false">B4-C4</f>
+        <v>6000</v>
+      </c>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5550</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A5,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <f aca="false">B5-C5</f>
+        <v>2050</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <f aca="false">B5-C5</f>
+        <v>2050</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>6600</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A6,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <f aca="false">B6-C6</f>
+        <v>2200</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>5950</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <f aca="false">ROUND(AVERAGEIF(Sales!$A:$A,A7,Sales!$I:$I),1)</f>
+        <v>36.7</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <f aca="false">B7-C7</f>
+        <v>2450</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <f aca="false">B7-C7</f>
+        <v>2450</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I10" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I11" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I12" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I13" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I14" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I16" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I17" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I18" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="6" t="n">
+        <f aca="false">B2-C2</f>
+        <v>1900</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>19</v>
@@ -464,7 +616,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
@@ -495,7 +647,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
@@ -526,7 +678,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>19</v>
@@ -557,7 +709,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>19</v>
@@ -588,7 +740,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>21</v>
@@ -619,7 +771,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>21</v>
@@ -650,7 +802,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>19</v>
@@ -681,7 +833,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>21</v>
@@ -712,7 +864,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>21</v>
@@ -743,7 +895,7 @@
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>21</v>
@@ -774,7 +926,7 @@
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
